--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,506 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128494283</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>549110</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7131934</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128494302</v>
+      </c>
+      <c r="B5" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>510</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549180</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7131957</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128494298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549116</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7131918</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128494271</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549194</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7131898</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128494297</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7131863</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128494302</v>
       </c>
       <c r="B5" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128494298</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>128494271</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128494297</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494298</v>
+        <v>128494271</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549116</v>
+        <v>549194</v>
       </c>
       <c r="R6" t="n">
-        <v>7131918</v>
+        <v>7131898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494271</v>
+        <v>128494298</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549194</v>
+        <v>549116</v>
       </c>
       <c r="R7" t="n">
-        <v>7131898</v>
+        <v>7131918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128494302</v>
       </c>
       <c r="B5" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494271</v>
+        <v>128494298</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549194</v>
+        <v>549116</v>
       </c>
       <c r="R6" t="n">
-        <v>7131898</v>
+        <v>7131918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494298</v>
+        <v>128494271</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549116</v>
+        <v>549194</v>
       </c>
       <c r="R7" t="n">
-        <v>7131918</v>
+        <v>7131898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1308,7 @@
         <v>128494297</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128494302</v>
       </c>
       <c r="B5" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494298</v>
+        <v>128494271</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549116</v>
+        <v>549194</v>
       </c>
       <c r="R6" t="n">
-        <v>7131918</v>
+        <v>7131898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494271</v>
+        <v>128494298</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549194</v>
+        <v>549116</v>
       </c>
       <c r="R7" t="n">
-        <v>7131898</v>
+        <v>7131918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128494302</v>
       </c>
       <c r="B5" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494271</v>
+        <v>128494298</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549194</v>
+        <v>549116</v>
       </c>
       <c r="R6" t="n">
-        <v>7131898</v>
+        <v>7131918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494298</v>
+        <v>128494271</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549116</v>
+        <v>549194</v>
       </c>
       <c r="R7" t="n">
-        <v>7131918</v>
+        <v>7131898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1308,7 @@
         <v>128494297</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128494302</v>
       </c>
       <c r="B5" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128494298</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>128494271</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128494297</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128494283</v>
       </c>
       <c r="B4" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128494302</v>
       </c>
       <c r="B5" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128494298</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128494297</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16817219</v>
+        <v>128494302</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>frostberget, Ång</t>
+          <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549212.5881791441</v>
+        <v>549180</v>
       </c>
       <c r="R2" t="n">
-        <v>7131877.963627128</v>
+        <v>7131957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,66 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16817220</v>
+        <v>128494283</v>
       </c>
       <c r="B3" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>frostberget, Ång</t>
+          <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549214.3647166386</v>
+        <v>549110</v>
       </c>
       <c r="R3" t="n">
-        <v>7131902.732266712</v>
+        <v>7131934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,48 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494283</v>
+        <v>128494297</v>
       </c>
       <c r="B4" t="n">
-        <v>91511</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549110</v>
+        <v>549200</v>
       </c>
       <c r="R4" t="n">
-        <v>7131934</v>
+        <v>7131863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494302</v>
+        <v>128494298</v>
       </c>
       <c r="B5" t="n">
-        <v>88915</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549180</v>
+        <v>549116</v>
       </c>
       <c r="R5" t="n">
-        <v>7131957</v>
+        <v>7131918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494298</v>
+        <v>104023186</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,34 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Frostberget, Ång</t>
+          <t>Passmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549116</v>
+        <v>549239</v>
       </c>
       <c r="R6" t="n">
-        <v>7131918</v>
+        <v>7131857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,17 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,22 +1168,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494271</v>
+        <v>16817219</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,34 +1195,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Frostberget, Ång</t>
+          <t>frostberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549194</v>
+        <v>549213</v>
       </c>
       <c r="R7" t="n">
-        <v>7131898</v>
+        <v>7131878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,17 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,57 +1269,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494297</v>
+        <v>16817220</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>80468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Frostberget, Ång</t>
+          <t>frostberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549200</v>
+        <v>549214</v>
       </c>
       <c r="R8" t="n">
-        <v>7131863</v>
+        <v>7131903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,17 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,15 +1370,223 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128494264</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549039</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7131926</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128494271</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549194</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7131898</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40013-2025 artfynd.xlsx
+++ b/artfynd/A 40013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494283</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494297</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023186</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817220</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,8 +1632,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>